--- a/arquivos_auxiliares/emails.xlsx
+++ b/arquivos_auxiliares/emails.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan Faita\Documents\GitHub\sof_adesampa\arquivos_auxiliares\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a3efe3a30af7d02/Documentos/GitHub/sof_adesampa/arquivos_auxiliares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB54A0D-EE31-4E33-B9C1-0BB816A08F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{4BB54A0D-EE31-4E33-B9C1-0BB816A08F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92EB9AC5-8102-4A1D-94D3-49E37BA6A111}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>nome</t>
   </si>
@@ -55,6 +55,27 @@
   </si>
   <si>
     <t>nathan.faita@adesampa.com.br</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Feminino</t>
+  </si>
+  <si>
+    <t>Assistente III</t>
+  </si>
+  <si>
+    <t>kelly.azevedo@adesampa.com.br</t>
+  </si>
+  <si>
+    <t>Natalia</t>
+  </si>
+  <si>
+    <t>Gerente</t>
+  </si>
+  <si>
+    <t>natalia.oliveira@adesampa.com.br</t>
   </si>
 </sst>
 </file>
@@ -108,8 +129,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -221,14 +242,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{007AA0F1-2BAE-403C-BE53-4AF5233D8E40}" name="Tabela1" displayName="Tabela1" ref="A1:E2" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:E2" xr:uid="{007AA0F1-2BAE-403C-BE53-4AF5233D8E40}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{007AA0F1-2BAE-403C-BE53-4AF5233D8E40}" name="Tabela1" displayName="Tabela1" ref="A1:E4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E4" xr:uid="{007AA0F1-2BAE-403C-BE53-4AF5233D8E40}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A82D25E9-DB6F-4534-AC70-D530ECFCA7D1}" name="nome" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{4F474395-8BC8-4DF9-A2E7-3988EA791490}" name="genero" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1915E8C5-0065-42F5-893C-1AA08FCA9A1C}" name="cargo" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{2924B4B7-D394-480F-82A9-31732AF7C2F3}" name="area" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{7A736CE7-2F02-43A4-AD08-05F0D30509B2}" name="email" dataDxfId="2" dataCellStyle="Hiperlink"/>
+    <tableColumn id="1" xr3:uid="{A82D25E9-DB6F-4534-AC70-D530ECFCA7D1}" name="nome" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{4F474395-8BC8-4DF9-A2E7-3988EA791490}" name="genero" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{1915E8C5-0065-42F5-893C-1AA08FCA9A1C}" name="cargo" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2924B4B7-D394-480F-82A9-31732AF7C2F3}" name="area" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{7A736CE7-2F02-43A4-AD08-05F0D30509B2}" name="email" dataDxfId="0" dataCellStyle="Hiperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -497,44 +518,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
